--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseEndReceiveError.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseEndReceiveError.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <r>
       <rPr>
@@ -75,6 +75,20 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>结束交货原因</t>
+    </r>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -82,6 +96,9 @@
   </si>
   <si>
     <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -97,7 +114,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +271,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1025,15 +1048,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="2" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1043,16 +1066,22 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
